--- a/pdf/Type-c port.xlsx
+++ b/pdf/Type-c port.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nvme\Desktop\新建文件夹 (5)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HTML合集\html文件本地包\pdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF776EB0-74A4-4CD8-81D1-FCFF639440F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83ABA3D2-71F8-4AE4-9471-DEB73E4336F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{ABC831A9-C5B2-40BF-9D24-BA283C288397}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{ABC831A9-C5B2-40BF-9D24-BA283C288397}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
   <si>
     <t>A1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -179,6 +179,14 @@
   </si>
   <si>
     <t>Sbu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5-56K-B9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B5-56K-A9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -186,18 +194,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -205,7 +213,7 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -258,9 +266,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -298,7 +306,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -404,7 +412,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -546,7 +554,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -554,13 +562,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743F4C09-C43D-4EB8-854A-5AFB1C7BAEBB}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,7 +606,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -636,7 +644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
@@ -674,7 +682,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -710,6 +718,14 @@
       </c>
       <c r="L5" s="1" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
